--- a/artfynd/A 49419-2023 artfynd.xlsx
+++ b/artfynd/A 49419-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122034784</v>
+        <v>122034667</v>
       </c>
       <c r="B2" t="n">
-        <v>58019</v>
+        <v>57708</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>103008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,7 +708,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670645</v>
+        <v>670490</v>
       </c>
       <c r="R2" t="n">
-        <v>6563066</v>
+        <v>6562904</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122034667</v>
+        <v>122034784</v>
       </c>
       <c r="B3" t="n">
-        <v>57708</v>
+        <v>58019</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,20 +802,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>103042</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,11 +823,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>670490</v>
+        <v>670645</v>
       </c>
       <c r="R3" t="n">
-        <v>6562904</v>
+        <v>6563066</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49419-2023 artfynd.xlsx
+++ b/artfynd/A 49419-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122034667</v>
+        <v>122034784</v>
       </c>
       <c r="B2" t="n">
-        <v>57708</v>
+        <v>58024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103008</v>
+        <v>103042</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,11 +708,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670490</v>
+        <v>670645</v>
       </c>
       <c r="R2" t="n">
-        <v>6562904</v>
+        <v>6563066</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122034784</v>
+        <v>122034667</v>
       </c>
       <c r="B3" t="n">
-        <v>58019</v>
+        <v>57713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,20 +798,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>103008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,7 +819,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>670645</v>
+        <v>670490</v>
       </c>
       <c r="R3" t="n">
-        <v>6563066</v>
+        <v>6562904</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49419-2023 artfynd.xlsx
+++ b/artfynd/A 49419-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122034784</v>
+        <v>119347660</v>
       </c>
       <c r="B2" t="n">
-        <v>58024</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>100067</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,21 +704,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björksättra, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670645</v>
+        <v>670362</v>
       </c>
       <c r="R2" t="n">
-        <v>6563066</v>
+        <v>6562860</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sågs flyga mellan tallarna</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,48 +765,43 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marlijn Sterenborg</t>
+          <t>Jörgen Wissman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Björklund</t>
+          <t>Jörgen Wissman, Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
+          <t>ESN0033 Björksättra NVI 2024</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122034667</v>
+        <v>119347603</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>100096</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,26 +809,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Björksättra, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>670490</v>
+        <v>670441</v>
       </c>
       <c r="R3" t="n">
-        <v>6562904</v>
+        <v>6562869</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,15 +866,553 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Jörgen Wissman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jörgen Wissman, Jacqueline Nelms</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>ESN0033 Björksättra NVI 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122034658</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58209</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102980</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ladusvala</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hirundo rustica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björksättra, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>670684</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6563019</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Marlijn Sterenborg</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Marie Björklund</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122034667</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58286</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björksättra, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>670490</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6562904</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marie Björklund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122034752</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björksättra, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>670487</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6562878</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marie Björklund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122034784</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björksättra, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>670645</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6563066</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marie Björklund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122034820</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björksättra, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>670637</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6563030</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marie Björklund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
         </is>

--- a/artfynd/A 49419-2023 artfynd.xlsx
+++ b/artfynd/A 49419-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>ESN0033 Björksättra NVI 2024</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119347660</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>ESN0033 Björksättra NVI 2024</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119347603</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
           <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122034658</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
           <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122034667</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
           <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122034752</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
           <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122034784</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,8 +1452,22 @@
           <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122034820</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>